--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24031.63</v>
+        <v>24208.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10501.58</v>
+        <v>10406.42</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>124323.82</v>
+        <v>123466.9</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13723.74</v>
+        <v>13941.02</v>
       </c>
     </row>
   </sheetData>
